--- a/data/qa/prospect_to_cash/opportunity.xlsx
+++ b/data/qa/prospect_to_cash/opportunity.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0002</t>
+          <t>KB-0089</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Opportunity</t>
+          <t>Opportunity Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Opportunities</t>
-        </is>
-      </c>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is an Opportunity?</t>
+          <t>What is an opportunity in the system?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>An Opportunity is a qualified potential sale being actively pursued, created once a Prospect or Lead shows real buying interest.</t>
+          <t>An opportunity represents a potential sale for a prospect or customer. It is the sales pipeline record, and includes details like party, salesperson or contact, status, stage, estimated value, chance of winning, projected close date, and won or lost reason.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>opportunity,deal</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>deal,potential sale</t>
-        </is>
-      </c>
+          <t>opportunity, pipeline, potential sale, Opportunities form</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>opportunity.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Opportunity Module &gt; Record meaning and form map</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,500 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0090</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_FIELD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>What information does the Opportunities form track?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The Opportunities form holds the party, salesperson or contact, status, stage, estimated value, chance of winning, projected close date, and won or lost reason. Related forms and tabs show tasks, estimates, orders, competitors, and team members.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Opportunities form, status, estimated value, projected close date</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>opportunity.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Opportunity Module &gt; Record meaning and form map</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0091</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I create and manage an opportunity?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ensure required Opportunity Statuses exist and configure sources, stages, task types, and win/loss reasons if used. From a lead or Opportunities, create a new record, select a prospect or customer, assign a salesperson or contact, set the initial status, estimated value, win chance, and projected close date, then save. Create Opportunity Tasks with a type, owner, priority, due date, and optional mandatory indicator. As the deal progresses, update stage, status, probability, and expected close date, and record the reason when won or lost.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>create opportunity, Opportunity Tasks, stage, status, estimated value</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>opportunity.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Opportunity Module &gt; Create and manage an opportunity</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0092</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I keep updated when managing an opportunity?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Keep status, probability, close date, tasks, and quote links current.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>status, probability, close date, tasks, quote links</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>opportunity.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Opportunity Module &gt; Create and manage an opportunity</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0093</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What is the difference between a won opportunity and a booked customer order?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A won opportunity is not automatically the same as a booked customer order; you must verify the customer, estimate, and order records separately.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>won opportunity, customer order, verification</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>opportunity.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Opportunity Module &gt; Forecast and handoff</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0094</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Opportunity Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>What steps are involved in converting a prospect win to a customer?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>For a prospect win, the process includes setting a won reason, moving the prospect to a customer, and verifying the customer.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>prospect win, customer conversion, verification</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>opportunity.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Opportunity Module &gt; Forecast and handoff</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,36 +1150,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -696,7 +1188,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0002</t>
+          <t>KB-0089</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -706,7 +1198,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>define opportunity</t>
+          <t>What does opportunity mean here?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -716,11 +1208,521 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0089</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>How is an opportunity defined?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0089</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>What is the purpose of an opportunity record?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0090</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>What fields are on the Opportunities form?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0090</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What details are tracked for an opportunity?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0090</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>What does the Opportunities form include?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0091</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to create and manage an opportunity?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0091</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I set up and track an opportunity?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0091</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Can you explain the process for handling opportunities?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0092</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What details need to be kept current for opportunities?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0092</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which fields should I update as an opportunity progresses?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0092</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What information should I maintain for each opportunity?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0093</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Is a won opportunity the same as a booked order?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0093</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Do I need to do anything after winning an opportunity before booking an order?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0093</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What's the process after an opportunity is marked as won?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0094</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How do I turn a prospect win into a customer?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0094</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What do I do after a prospect is won?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0094</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Steps to convert a won prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
